--- a/Project-Group4 - Copy.xlsx
+++ b/Project-Group4 - Copy.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Digilians\grades\Group 4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nouran Ahmed\OneDrive\Desktop\Digilians-Group4-Frontend-Nti\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="81">
   <si>
     <t>Last name</t>
   </si>
@@ -264,6 +264,9 @@
   </si>
   <si>
     <t>https://www.figma.com/design/9OBHJ3aPUFvKId2dlOk3vP/E-Commerce-Complete-UI-Kit--Desktop---Mobile---Community-?node-id=1-3&amp;p=f&amp;t=3ho1lhJDtZDsSHzK-0</t>
+  </si>
+  <si>
+    <t>https://www.figma.com/design/9OBHJ3aPUFvKId2dlOk3vP/E-Commerce-Complete-UI-Kit--Desktop---Mobile---Community-?node-id=1-3&amp;p=f&amp;t=WY54CLz3rrLR6H8f-0</t>
   </si>
 </sst>
 </file>
@@ -339,11 +342,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Good" xfId="1" builtinId="26"/>
@@ -636,12 +639,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="4"/>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="3"/>
     </row>
     <row r="2" spans="1:4" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
@@ -667,7 +670,7 @@
       <c r="C3" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="4" t="s">
         <v>78</v>
       </c>
     </row>
@@ -737,8 +740,8 @@
       <c r="C8" t="s">
         <v>51</v>
       </c>
-      <c r="D8" t="s">
-        <v>76</v>
+      <c r="D8" s="4" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
@@ -779,7 +782,7 @@
       <c r="C11" t="s">
         <v>10</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="D11" s="4" t="s">
         <v>78</v>
       </c>
     </row>
@@ -807,7 +810,7 @@
       <c r="C13" t="s">
         <v>29</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="D13" s="4" t="s">
         <v>78</v>
       </c>
     </row>
@@ -919,7 +922,7 @@
       <c r="C21" t="s">
         <v>21</v>
       </c>
-      <c r="D21" s="5" t="s">
+      <c r="D21" s="4" t="s">
         <v>78</v>
       </c>
     </row>
@@ -947,7 +950,7 @@
       <c r="C23" t="s">
         <v>24</v>
       </c>
-      <c r="D23" s="5" t="s">
+      <c r="D23" s="4" t="s">
         <v>78</v>
       </c>
     </row>
@@ -1011,10 +1014,10 @@
       <c r="C28" t="s">
         <v>70</v>
       </c>
-      <c r="D28" s="5"/>
+      <c r="D28" s="4"/>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D31" s="5"/>
+      <c r="D31" s="4"/>
     </row>
   </sheetData>
   <sortState ref="A3:D28">
@@ -1029,8 +1032,9 @@
     <hyperlink ref="D13" r:id="rId3"/>
     <hyperlink ref="D21" r:id="rId4"/>
     <hyperlink ref="D23" r:id="rId5"/>
+    <hyperlink ref="D8" r:id="rId6"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId6"/>
+  <pageSetup orientation="portrait" r:id="rId7"/>
 </worksheet>
 </file>